--- a/templates/recibo_template.xlsx
+++ b/templates/recibo_template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C27E0B1-914A-4D33-B6DF-BEC4950AB518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2563C8D4-F2EB-4FE6-A120-D541756AF223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="44">
   <si>
     <t>First Up Consultants</t>
   </si>
@@ -111,12 +111,6 @@
   </si>
   <si>
     <t>Service fee</t>
-  </si>
-  <si>
-    <t>Labor: 5 hours at $75/hr</t>
-  </si>
-  <si>
-    <t>New client discount</t>
   </si>
   <si>
     <t>← The QTY is assumed to be 1 if it is left blank</t>
@@ -1742,37 +1736,21 @@
       <c r="H16" s="22"/>
     </row>
     <row r="17" spans="2:8" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="36" t="s">
-        <v>29</v>
-      </c>
+      <c r="B17" s="36"/>
       <c r="C17" s="37"/>
-      <c r="D17" s="38">
-        <v>5</v>
-      </c>
-      <c r="E17" s="39">
-        <v>75</v>
-      </c>
-      <c r="F17" s="40">
-        <f t="shared" ref="F17:F30" si="0">IF(D17="",ROUND(1*E17,2),ROUND(D17*E17,2))</f>
-        <v>375</v>
-      </c>
+      <c r="D17" s="38"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="40"/>
       <c r="H17" s="22"/>
     </row>
     <row r="18" spans="2:8" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="36" t="s">
-        <v>30</v>
-      </c>
+      <c r="B18" s="36"/>
       <c r="C18" s="37"/>
       <c r="D18" s="38"/>
-      <c r="E18" s="39">
-        <v>-50</v>
-      </c>
-      <c r="F18" s="40">
-        <f t="shared" si="0"/>
-        <v>-50</v>
-      </c>
+      <c r="E18" s="39"/>
+      <c r="F18" s="40"/>
       <c r="H18" s="22" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="2:8" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1781,7 +1759,7 @@
       <c r="D19" s="38"/>
       <c r="E19" s="39"/>
       <c r="F19" s="40">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F17:F30" si="0">IF(D19="",ROUND(1*E19,2),ROUND(D19*E19,2))</f>
         <v>0</v>
       </c>
       <c r="H19" s="30"/>
@@ -1909,16 +1887,16 @@
     </row>
     <row r="31" spans="2:8" s="8" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B31" s="63" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C31" s="63"/>
       <c r="D31" s="64" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E31" s="64"/>
       <c r="F31" s="45">
         <f>SUM(F16:F30)</f>
-        <v>525</v>
+        <v>200</v>
       </c>
       <c r="H31" s="22"/>
     </row>
@@ -1926,26 +1904,26 @@
       <c r="B32" s="23"/>
       <c r="C32" s="16"/>
       <c r="D32" s="64" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E32" s="64"/>
       <c r="F32" s="46">
         <v>4.2500000000000003E-2</v>
       </c>
       <c r="H32" s="22" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="23"/>
       <c r="C33" s="16"/>
       <c r="D33" s="23" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E33" s="23"/>
       <c r="F33" s="45">
         <f>F31*F32</f>
-        <v>22.3125</v>
+        <v>8.5</v>
       </c>
       <c r="H33" s="22"/>
     </row>
@@ -1953,15 +1931,15 @@
       <c r="B34" s="47"/>
       <c r="C34" s="48"/>
       <c r="D34" s="49" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E34" s="57"/>
       <c r="F34" s="58">
         <f>F31+F33</f>
-        <v>547.3125</v>
+        <v>208.5</v>
       </c>
       <c r="H34" s="22" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35" spans="2:8" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1971,7 +1949,7 @@
       <c r="E35" s="50"/>
       <c r="F35" s="50"/>
       <c r="H35" s="22" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="36" spans="2:8" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1984,7 +1962,7 @@
     </row>
     <row r="37" spans="2:8" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="65" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C37" s="65"/>
       <c r="D37" s="65"/>
@@ -1994,14 +1972,14 @@
     </row>
     <row r="38" spans="2:8" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="61" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C38" s="61"/>
       <c r="D38" s="61"/>
       <c r="E38" s="61"/>
       <c r="F38" s="61"/>
       <c r="H38" s="22" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39" spans="2:8" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -2067,12 +2045,12 @@
     <row r="4" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:2" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15" x14ac:dyDescent="0.25">
@@ -2080,7 +2058,7 @@
     </row>
     <row r="8" spans="1:2" ht="82.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -2095,15 +2073,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="30" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="cec0622158e8f13124e9e8fd4de31bd1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3b52f30ab005d15df08657af532e6e38" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -2421,6 +2390,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -2442,14 +2420,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C42C6076-3E7F-4885-A017-B36671B5853A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{368254F9-4B70-4B70-9250-7541232C303C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2470,6 +2440,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C42C6076-3E7F-4885-A017-B36671B5853A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D626D1C8-EC9A-4213-BF72-F97E82B4EAAA}">
   <ds:schemaRefs>
